--- a/evalpicker/data/evaluation_approaches.xlsx
+++ b/evalpicker/data/evaluation_approaches.xlsx
@@ -2745,7 +2745,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -3060,6 +3060,162 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>modal_what_you_get</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>What you get</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>modal_wont_tell</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>What it will not tell you</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>modal_required_data</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Data you need</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>modal_origin</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Where it comes from</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>modal_values</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>A note on values</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>modal_sources</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>modal_chain</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>What has to come first</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>modal_verdict</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>For what you set right now</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>modal_close</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>verdict_fits</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>This fits what you told us.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>verdict_unlock</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Not yet. The gap is below.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>verdict_out</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>This is not the right tool for what you picked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>modal_hint</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Click any card for the full picture.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/evalpicker/data/evaluation_approaches.xlsx
+++ b/evalpicker/data/evaluation_approaches.xlsx
@@ -2745,7 +2745,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B39"/>
+  <dimension ref="A1:B63"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2763,456 +2763,744 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>page_title</t>
+          <t>page_sub</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Which Evaluation Should We Do?</t>
+          <t>datawithaplot.org · matching the method to the question</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>page_sub</t>
+          <t>intro_eyebrow</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Set what you have and what you want. The tool sorts every approach into what fits, what is close, and what is the wrong tool, and it says why every time.</t>
+          <t>Seven questions</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>scope_note</t>
+          <t>intro_title</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>This is a starting point for a conversation with an evaluator, not a substitute for one. It narrows the field and explains the tradeoffs. It does not know your program.</t>
+          <t>Most of the field is wrong for you.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>heading_fits</t>
+          <t>intro_lead</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>These fit what you have</t>
+          <t>That is the useful part. Answer seven questions about your program, your data and your audience, and every approach sorts itself into what fits, what is close, and what is the wrong tool. Nothing lands in a pile without a reason attached.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>heading_unlock</t>
+          <t>intro_btn</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>These are close</t>
+          <t>Start the seven questions →</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>heading_unlock_sub</t>
+          <t>intro_note</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Each of these needs something you do not have yet. The gap is named, and so is what it takes to close it.</t>
+          <t>Takes about two minutes. Nothing you enter leaves your browser.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>heading_out</t>
+          <t>zero_prompt</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>These are not the right tool here</t>
+          <t>Answer any one of the seven and the field sorts itself.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>heading_out_sub</t>
+          <t>scope_note</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Not because you lack resources. These answer a different question than the one you picked.</t>
+          <t>This is a starting point for a conversation with an evaluator, not a substitute for one. It narrows the field and explains the tradeoffs. It does not know your program.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>empty_fits</t>
+          <t>filter_any</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Nothing fits every constraint you set. The closest options are below, with the gap named.</t>
+          <t>Any</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>reason_audience_ok</t>
+          <t>filter_clear</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{approach} is not written for {have}. It is built for: {needed}.</t>
+          <t>Clear</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>reason_purpose_ok</t>
+          <t>done_label</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>You picked "{have}". {approach} is built for: {needed}.</t>
+          <t>Already done</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>reason_question_ok</t>
+          <t>tab_approaches</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{approach} does not answer "{have}". It answers: {needed}.</t>
+          <t>Evaluation approaches</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>reason_maturity_min</t>
+          <t>tab_tmfs</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{approach} needs a program that has been running longer. Yours is {have}. This needs at least {needed}.</t>
+          <t>Implementation frameworks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>reason_maturity_max</t>
+          <t>stats_fits</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{approach} is built for a program that is still taking shape. Yours is {have}.</t>
+          <t>fit</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>reason_data_level_min</t>
+          <t>stats_unlock</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{approach} needs {needed}. You said you can get {have}.</t>
+          <t>close</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>reason_comparison_required</t>
+          <t>stats_out</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{approach} needs a comparison group, and you said you do not have one.</t>
+          <t>not the right tool</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>reason_fidelity_ok</t>
+          <t>btn_print</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{approach} does not suit this program. You said: {have}.</t>
+          <t>Print this shortlist</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>note_comparison_recommended</t>
+          <t>modal_hint</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>A comparison group is not required here, but without one you cannot say the program caused the result.</t>
+          <t>Click any card for the full picture.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>note_comparison_unsure</t>
+          <t>heading_fits</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Worth pinning down whether you have a comparison group. It changes what is possible here.</t>
+          <t>These fit what you have</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>prereq_required_lead</t>
+          <t>heading_fits_sub</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>You have to do this first:</t>
+          <t>Nothing you said rules these out. The ones that ask least of your data come first.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>prereq_advise_lead</t>
+          <t>heading_unlock</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Worth doing first:</t>
+          <t>These are close</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>steps_away</t>
+          <t>heading_unlock_sub</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{n} steps away</t>
+          <t>Each of these needs something you do not have yet. The gap is named, and so is what it takes to close it.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>steps_away_one</t>
+          <t>heading_out</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1 step away</t>
+          <t>These are not the right tool here</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>label_burden</t>
+          <t>heading_out_sub</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Data burden</t>
+          <t>Not because you lack resources. These answer a different question than the one you asked.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>label_timeline</t>
+          <t>empty_fits</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Typical timeline</t>
+          <t>Nothing fits everything you said. The closest options are below, with the gap named.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>modal_what_you_get</t>
+          <t>empty_unlock</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>What you get</t>
+          <t>Nothing is waiting on anything you do not have.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>modal_wont_tell</t>
+          <t>empty_out</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>What it will not tell you</t>
+          <t>Nothing here is the wrong tool for what you said.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>modal_required_data</t>
+          <t>label_burden</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Data you need</t>
+          <t>{level} data burden</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>modal_origin</t>
+          <t>label_timeline</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Where it comes from</t>
+          <t>Typical timeline</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>modal_values</t>
+          <t>gap_lead_missing</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>A note on values</t>
+          <t>Missing</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>modal_sources</t>
+          <t>gap_lead_whynot</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Sources</t>
+          <t>Why not</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>modal_chain</t>
+          <t>steps_away</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>What has to come first</t>
+          <t>{n} steps away</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>modal_verdict</t>
+          <t>steps_away_one</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>For what you set right now</t>
+          <t>1 step away</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>modal_close</t>
+          <t>prereq_required_lead</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Close</t>
+          <t>You have to do this first:</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>verdict_fits</t>
+          <t>prereq_advise_lead</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>This fits what you told us.</t>
+          <t>Worth doing first:</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>verdict_unlock</t>
+          <t>chain_must</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Not yet. The gap is below.</t>
+          <t>has to come first.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>verdict_out</t>
+          <t>chain_done</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>This is not the right tool for what you picked.</t>
+          <t>already done</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>modal_hint</t>
+          <t>chain_advise</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Click any card for the full picture.</t>
+          <t>worth doing first</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>chain_required</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>required first</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>chain_notneeded</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>not needed here</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>modal_verdict</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>For what you have said so far</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>verdict_fits</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>This fits what you said.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>verdict_unlock</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Not yet. The gap is below.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>verdict_out</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>This is not the right tool for what you said.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>modal_what_you_get</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>What you get</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>modal_wont_tell</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>What it will not tell you</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>modal_required_data</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Data you need</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>modal_chain</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>What has to come first</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>modal_origin</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Where it comes from</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>modal_values</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>A note on values</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>modal_sources</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>modal_close</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>reason_audience_ok</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>{approach} is not written for {have}. It is built for: {needed}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>reason_purpose_ok</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>You said "{have}". {approach} is built for: {needed}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>reason_question_ok</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>{approach} does not answer "{have}". It answers: {needed}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>reason_maturity_min</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>{approach} needs a program that has been running longer. Yours is {have}. This needs at least {needed}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>reason_maturity_max</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>{approach} is built for a program that is still taking shape. Yours is {have}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>reason_data_level_min</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>{approach} needs {needed}. You said you can get {have}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>reason_comparison_required</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>{approach} needs a comparison group, and you said you do not have one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>reason_fidelity_ok</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>{approach} does not suit this program. You said: {have}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>note_comparison_recommended</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>A comparison group is not required here, but without one you cannot say the program caused the result.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>note_comparison_unsure</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Worth pinning down whether you have a comparison group. It changes what is possible here.</t>
         </is>
       </c>
     </row>

--- a/evalpicker/data/evaluation_approaches.xlsx
+++ b/evalpicker/data/evaluation_approaches.xlsx
@@ -654,7 +654,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -932,7 +932,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Running as designed</t>
+          <t>What is needed</t>
         </is>
       </c>
       <c r="C14">
@@ -940,7 +940,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Is it running the way we designed it?</t>
+          <t>What do people actually need?</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Who we reach</t>
+          <t>Ready to evaluate</t>
         </is>
       </c>
       <c r="C15">
@@ -960,7 +960,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Who are we reaching, and who are we missing?</t>
+          <t>Is the program ready to be evaluated?</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Did they change</t>
+          <t>Running as designed</t>
         </is>
       </c>
       <c r="C16">
@@ -980,7 +980,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Did participants change?</t>
+          <t>Is it running the way we designed it?</t>
         </is>
       </c>
     </row>
@@ -992,7 +992,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Did we cause it</t>
+          <t>Who we reach</t>
         </is>
       </c>
       <c r="C17">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Did the program cause the change?</t>
+          <t>Who are we reaching, and who are we missing?</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>For whom</t>
+          <t>What to change</t>
         </is>
       </c>
       <c r="C18">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>What works, for whom, in what circumstances?</t>
+          <t>What should we change?</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cost to run</t>
+          <t>Did they change</t>
         </is>
       </c>
       <c r="C19">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>What does it cost to run?</t>
+          <t>Did participants change?</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cost per result</t>
+          <t>Did we cause it</t>
         </is>
       </c>
       <c r="C20">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>What does it cost per result?</t>
+          <t>Did the program cause the change?</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Worth in dollars</t>
+          <t>For whom</t>
         </is>
       </c>
       <c r="C21">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>What is it worth in dollars?</t>
+          <t>What works, for whom, in what circumstances?</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>What to change</t>
+          <t>Cost to run</t>
         </is>
       </c>
       <c r="C22">
@@ -1100,52 +1100,47 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>What should we change?</t>
+          <t>What does it cost to run?</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>maturity</t>
+          <t>question</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>New or pilot</t>
+          <t>Cost per result</t>
         </is>
       </c>
       <c r="C23">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>New or pilot (under a year)</t>
+          <t>What does it cost per result?</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>maturity</t>
+          <t>question</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Getting established</t>
+          <t>Worth in dollars</t>
         </is>
       </c>
       <c r="C24">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Getting established (1 to 2 years)</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Give it another year of intake.</t>
+          <t>What is it worth in dollars?</t>
         </is>
       </c>
     </row>
@@ -1157,20 +1152,15 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Established</t>
+          <t>New or pilot</t>
         </is>
       </c>
       <c r="C25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Established (3 to 4 years)</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Wait until the program has run long enough to have a stable group of people who finished. Most impact designs need about three years of intake before the numbers hold.</t>
+          <t>New or pilot (under a year)</t>
         </is>
       </c>
     </row>
@@ -1182,65 +1172,70 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Mature</t>
+          <t>Getting established</t>
         </is>
       </c>
       <c r="C26">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Mature (5 or more years)</t>
+          <t>Getting established (1 to 2 years)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>This one needs several more years of operation.</t>
+          <t>Give it another year of intake.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>data_capacity</t>
+          <t>maturity</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Aggregate</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Counts only (how many served, how many finished)</t>
+          <t>Established (3 to 4 years)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Wait until the program has run long enough to have a stable group of people who finished. Most impact designs need about three years of intake before the numbers hold.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>data_capacity</t>
+          <t>maturity</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Participant</t>
+          <t>Mature</t>
         </is>
       </c>
       <c r="C28">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Participant-level program records</t>
+          <t>Mature (5 or more years)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Start keeping participant-level records: intake date, services received, exit status, exit date. This is mostly a data entry habit, not a system purchase.</t>
+          <t>This one needs several more years of operation.</t>
         </is>
       </c>
     </row>
@@ -1252,65 +1247,65 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Multi-agency</t>
+          <t>Aggregate</t>
         </is>
       </c>
       <c r="C29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Multi-agency records on individuals over time</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Set up data sharing agreements for the records you need: re-arrest, jail bed days, emergency room use, employment. This is the long pole. Start it a year before you need the data.</t>
+          <t>Counts only (how many served, how many finished)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>comparison</t>
+          <t>data_capacity</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Participant</t>
         </is>
       </c>
       <c r="C30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Participant-level program records</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Start keeping participant-level records: intake date, services received, exit status, exit date. This is mostly a data entry habit, not a system purchase.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>comparison</t>
+          <t>data_capacity</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Multi-agency</t>
         </is>
       </c>
       <c r="C31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Multi-agency records on individuals over time</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Find a comparison group. Options that work in courts: people who were eligible but did not enroll, a waitlist, a neighboring court, or your own court in the years before the program started.</t>
+          <t>Set up data sharing agreements for the records you need: re-arrest, jail bed days, emergency room use, employment. This is the long pole. Start it a year before you need the data.</t>
         </is>
       </c>
     </row>
@@ -1322,55 +1317,60 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Not sure</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="C32">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Not sure</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>fidelity</t>
+          <t>comparison</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Faithful</t>
+          <t>No</t>
         </is>
       </c>
       <c r="C33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>It follows an evidence-based model closely</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Find a comparison group. Options that work in courts: people who were eligible but did not enroll, a waitlist, a neighboring court, or your own court in the years before the program started.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>fidelity</t>
+          <t>comparison</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Adapted</t>
+          <t>Not sure</t>
         </is>
       </c>
       <c r="C34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>It started from a model but we changed things</t>
+          <t>Not sure</t>
         </is>
       </c>
     </row>
@@ -1382,15 +1382,15 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>Faithful</t>
         </is>
       </c>
       <c r="C35">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>We designed it ourselves</t>
+          <t>It follows an evidence-based model closely</t>
         </is>
       </c>
     </row>
@@ -1402,13 +1402,53 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
+          <t>Adapted</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>2</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>It started from a model but we changed things</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>fidelity</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>3</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>We designed it ourselves</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>fidelity</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
           <t>Not sure</t>
         </is>
       </c>
-      <c r="C36">
+      <c r="C38">
         <v>4</v>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>Not sure</t>
         </is>
@@ -1421,7 +1461,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AB8"/>
+  <dimension ref="A1:AB18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2222,6 +2262,916 @@
       <c r="AB8" t="inlineStr">
         <is>
           <t>Patton, Developmental Evaluation</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NEEDS</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Needs Assessment</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Groundwork</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Establishes what the population actually needs, and whether the program anyone is proposing would meet it.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Program staff; Court leadership; Partner agencies; Funders; Legislators</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Improve; Learn; Account</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>What is needed</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Aggregate</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Not needed</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>4 to 8 months</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Counts on the population you intend to serve, what services already exist, and what the people in it say they need. Administrative data plus asking.</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>A defensible statement of the gap between what people need and what they can currently get, which is the thing a new program is supposed to close.</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Whether your program is the answer. It sizes the problem. Choosing the response is a separate argument.</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Pragmatist</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Need is defined by somebody. Counting what the court finds inconvenient and counting what participants find unbearable produce different programs.</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>Altschuld &amp; Kumar, Needs Assessment</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EVALABILITY</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Evaluability Assessment</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Groundwork</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Checks whether the program is defined well enough to evaluate at all, before anyone spends a year finding out that it was not.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Program staff; Court leadership; Partner agencies; Funders</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Improve; Learn</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Ready to evaluate</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Aggregate</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Not needed</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2 to 4 months</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Program documents, the logic as staff actually describe it, and a look at what data already exists. No new collection.</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>A clear answer on whether an evaluation can succeed yet, and a list of what to fix first if it cannot.</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Whether the program works. It tells you whether that question can currently be answered.</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Pragmatist</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Deciding a program is not ready to evaluate can shield it from scrutiny as easily as it can spare the evaluation from waste. Who asked for the assessment matters.</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>Wholey, Evaluability Assessment</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>THEORY</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Theory-Driven Evaluation</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Explanatory</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Writes down the chain from what the program does to what it expects to change, then tests the links one at a time.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Program staff; Court leadership; Partner agencies; Funders</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Improve; Learn; Share</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Ready to evaluate; Running as designed; Did we cause it</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Aggregate</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Not needed</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>6 to 12 months</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Program documents and staff accounts to build the model, then whatever each link needs to test. Often aggregate for the early links and participant-level for the later ones.</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>A model of how the program is supposed to work, and evidence on which links hold and which break.</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Whether an untested link is sound. A theory nobody has checked against data is a diagram, not a finding.</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Post-positivist, theory-driven</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>The theory comes from somewhere, usually from the people who designed the program. Their assumptions get built into what you then go and measure.</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>Chen, Theory-Driven Evaluations</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>FORMATIVE</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Formative Evaluation</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Learning and adaptation</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Feeds findings back while the program is still taking shape, so the design can change before it hardens.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Program staff; Court leadership; Partner agencies</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Improve; Learn</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Running as designed; What to change</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Established</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Aggregate</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Not needed</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>3 to 9 months</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Early implementation data, staff and participant feedback, and whatever counts you already keep. Speed matters more than completeness.</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Specific changes to the design, delivered while changing it is still cheap.</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Whether the finished program works. Formative work stops where the summative question starts.</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Pragmatist</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Improving a program assumes the program should exist. Formative evaluation rarely asks that, and it is worth asking out loud once.</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Formative work is for a program that can still change its design. On a settled program it produces suggestions nobody is in a position to act on.</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>Scriven, The Methodology of Evaluation</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>RAPID</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Rapid Cycle Evaluation</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Learning and adaptation</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Runs short test-and-adjust loops on one piece of the program and answers in weeks rather than years.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Program staff; Court leadership</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Improve; Learn</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>What to change</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Participant</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Not needed</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>6 to 12 weeks per cycle</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>One clearly defined change, a measure you can read quickly, and participant-level records that update often enough to see movement.</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Fast evidence on a specific change, and a habit of testing rather than arguing.</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Whether the program as a whole works. Short loops answer small questions well and large ones badly.</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Pragmatist, improvement science</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>What you can measure quickly is not what matters most. The speed of the loop quietly picks the outcomes.</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>Shrank, rapid-cycle evaluation blueprint (2013)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EMPOWER</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Empowerment Evaluation</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Learning and adaptation</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Hands the evaluation to the people running and using the program, with the evaluator as coach rather than judge.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Program staff; Court leadership; Participants</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Improve; Learn</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>What to change</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Aggregate</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Not needed</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Adapted; Local; Not sure</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Ongoing, built into how the program runs</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Whatever the group decides matters, gathered by the group. Usually a self-assessment, a plan they own, and a standing meeting where they check their own progress.</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>A program that can evaluate itself after you leave, and findings the staff and participants already believe because they produced them.</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Anything an outside reader will treat as independent. The credibility that comes from distance is exactly what this trades away.</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Participatory</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>This one takes a side on purpose: it holds that the people in a program have a right to judge it. That is a value position, not a method detail.</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Empowerment evaluation gives the group room to change the program. On a faithful implementation of somebody else's model there is little room to give.</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>Fetterman, Empowerment Evaluation</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>UFE</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Utilization-Focused Evaluation</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Learning and adaptation</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Starts from who will actually use the findings and what they will do with them, then designs the evaluation backwards from that.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Program staff; Court leadership; Partner agencies; Funders; Legislators; Participants</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Improve; Learn; Account; Continue; Value; Share</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Ready to evaluate; What to change</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Aggregate</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Not needed</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Runs alongside whatever design you pick</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Whatever the intended users need. The method is chosen last, after the use is settled, so the data requirement is not fixed in advance.</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>An evaluation somebody actually uses, because the people who will act on it helped decide what it would answer.</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Anything, on its own. This is a way of choosing and running a design, not a design. It sits on top of whatever you pick.</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Pragmatist</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Designing around the intended users hands them the questions. Whoever is not in the room when the questions are set does not get answered.</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>Utilization-Focused Evaluation is a way of choosing and running a design, not a design of its own. It sits on top of whatever you pick, so it does not answer this on its own.</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>Patton, Utilization-Focused Evaluation</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CONTRIB</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Contribution Analysis</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Explanatory</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Builds the case that the program contributed to the change, and tests it against the other explanations, when a comparison group is impossible.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Court leadership; Partner agencies; Funders; Legislators</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Account; Continue; Share</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Did we cause it</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Getting established</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Participant</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Not needed</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>9 to 18 months</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>A written theory of change, participant-level outcomes over time, and enough context data to test the rival explanations rather than wave at them.</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>A reasoned, evidenced case for the program's contribution, with the alternative explanations named and addressed one at a time.</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>How much of the change was the program. You get a defensible argument, not an effect size, and a hostile reader can still disagree with it.</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Generative causation</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>You decide which rival explanations deserve testing. The one you decline to name is the one that undoes the finding later.</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>Mayne, Contribution Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>REALIST</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Realist Evaluation</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Explanatory</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Asks who the program works for, in what circumstances, and through what mechanism, rather than whether it works on average.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Program staff; Court leadership; Partner agencies; Funders</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Improve; Learn; Share</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>For whom</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Getting established</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Participant</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Not needed</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>12 to 24 months</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Participant-level outcomes, plus enough about context and about how people experienced the program to tell one subgroup's story from another's. Interviews carry most of the weight.</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Statements of the form: in this context, for these people, the program sets off this mechanism and produces this result. Where it does not fire, you learn that too.</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>A single number for the whole program. If the court wants one effect size for the annual report, this is the wrong tool.</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Realist</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>You choose which contexts and which subgroups are worth explaining. The groups left out of the design stay invisible in the findings.</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>Pawson &amp; Tilley, Realistic Evaluation (1997)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CUA</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Cost-Utility Analysis</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Economic</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Prices the program against a quality-weighted unit, so two results that are not alike can still be set against each other.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Court leadership; Funders; Legislators</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Continue; Value</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Cost per result</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Established</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Participant</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Recommended</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>6 to 12 months</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>All the direct costs, participant-level outcomes, and an agreed weighting for how much better one outcome is than another.</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>A cost per weighted unit that lets you compare programs chasing different results, which cost-effectiveness cannot do.</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Whether the weights are right. The whole comparison rests on them, and they are a judgment wearing a decimal point.</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Post-positivist, economic</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Someone decides how much a year of sobriety is worth against a year of housing. That number is a value claim, and putting it in a spreadsheet does not make it arithmetic.</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>Types of Cost Evaluations (Wylie)</t>
         </is>
       </c>
     </row>
@@ -2573,7 +3523,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2735,6 +3685,82 @@
       <c r="F6" t="inlineStr">
         <is>
           <t>The cost side of a cost-benefit study is a cost analysis. If you have already done one, you are not starting from nothing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CONTRIB</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PROCESS</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Conditional</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>fidelity</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Adapted; Local; Not sure</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Contribution analysis argues from what the program actually delivered to what changed. If you do not know what was delivered, the argument has no first step.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CUA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>OUTCOME</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Recommended</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Cost per weighted result needs the results. Without outcome data you have a cost and a weighting scheme with nothing to weight.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>IMPACT</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>EVALABILITY</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Recommended</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>An evaluability assessment is a cheap way to learn the program is not ready, before eighteen months of impact work proves the same thing expensively.</t>
         </is>
       </c>
     </row>
@@ -2745,7 +3771,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B63"/>
+  <dimension ref="A1:B69"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -3111,396 +4137,468 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>gap_lead_missing</t>
+          <t>steps_away</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>{n} steps away</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>gap_lead_whynot</t>
+          <t>steps_away_one</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Why not</t>
+          <t>1 step away</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>steps_away</t>
+          <t>prereq_advise_lead</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{n} steps away</t>
+          <t>Worth doing first:</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>steps_away_one</t>
+          <t>chain_must</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1 step away</t>
+          <t>has to come first.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>prereq_required_lead</t>
+          <t>chain_done</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>You have to do this first:</t>
+          <t>already done</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>prereq_advise_lead</t>
+          <t>chain_advise</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Worth doing first:</t>
+          <t>worth doing first</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>chain_must</t>
+          <t>chain_required</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>has to come first.</t>
+          <t>required first</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>chain_done</t>
+          <t>chain_notneeded</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>already done</t>
+          <t>not needed here</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>chain_advise</t>
+          <t>modal_verdict</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>worth doing first</t>
+          <t>For what you have said so far</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>chain_required</t>
+          <t>verdict_fits</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>required first</t>
+          <t>This fits what you said.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>chain_notneeded</t>
+          <t>verdict_unlock</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>not needed here</t>
+          <t>Not yet. The gap is below.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>modal_verdict</t>
+          <t>verdict_out</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>For what you have said so far</t>
+          <t>This is not the right tool for what you said.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>verdict_fits</t>
+          <t>modal_what_you_get</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>This fits what you said.</t>
+          <t>What you get</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>verdict_unlock</t>
+          <t>modal_wont_tell</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Not yet. The gap is below.</t>
+          <t>What it will not tell you</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>verdict_out</t>
+          <t>modal_required_data</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>This is not the right tool for what you said.</t>
+          <t>Data you need</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>modal_what_you_get</t>
+          <t>modal_chain</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>What you get</t>
+          <t>What has to come first</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>modal_wont_tell</t>
+          <t>modal_origin</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>What it will not tell you</t>
+          <t>Where it comes from</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>modal_required_data</t>
+          <t>modal_values</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Data you need</t>
+          <t>A note on values</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>modal_chain</t>
+          <t>modal_sources</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>What has to come first</t>
+          <t>Sources</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>modal_origin</t>
+          <t>modal_close</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Where it comes from</t>
+          <t>Close</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>modal_values</t>
+          <t>reason_audience_ok</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>A note on values</t>
+          <t>{approach} is not written for {have}. It is built for: {needed}.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>modal_sources</t>
+          <t>reason_purpose_ok</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Sources</t>
+          <t>You said "{have}". {approach} is built for: {needed}.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>modal_close</t>
+          <t>reason_question_ok</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Close</t>
+          <t>{approach} does not answer "{have}". It answers: {needed}.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>reason_audience_ok</t>
+          <t>reason_maturity_min</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{approach} is not written for {have}. It is built for: {needed}.</t>
+          <t>{approach} needs a program that has been running longer. Yours is {have}. This needs at least {needed}.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>reason_purpose_ok</t>
+          <t>reason_maturity_max</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>You said "{have}". {approach} is built for: {needed}.</t>
+          <t>{approach} is built for a program that is still taking shape. Yours is {have}.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>reason_question_ok</t>
+          <t>reason_data_level_min</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{approach} does not answer "{have}". It answers: {needed}.</t>
+          <t>{approach} needs {needed}. You said you can get {have}.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>reason_maturity_min</t>
+          <t>reason_comparison_required</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{approach} needs a program that has been running longer. Yours is {have}. This needs at least {needed}.</t>
+          <t>{approach} needs a comparison group, and you said you do not have one.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>reason_maturity_max</t>
+          <t>reason_fidelity_ok</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{approach} is built for a program that is still taking shape. Yours is {have}.</t>
+          <t>{approach} does not suit this program. You said: {have}.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>reason_data_level_min</t>
+          <t>note_comparison_recommended</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{approach} needs {needed}. You said you can get {have}.</t>
+          <t>A comparison group is not required here, but without one you cannot say the program caused the result.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>reason_comparison_required</t>
+          <t>note_comparison_unsure</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{approach} needs a comparison group, and you said you do not have one.</t>
+          <t>Worth pinning down whether you have a comparison group. It changes what is possible here.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>reason_fidelity_ok</t>
+          <t>short_prereq</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{approach} does not suit this program. You said: {have}.</t>
+          <t>{name} first</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>note_comparison_recommended</t>
+          <t>short_audience_ok</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>A comparison group is not required here, but without one you cannot say the program caused the result.</t>
+          <t>Written for a different audience</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>note_comparison_unsure</t>
+          <t>short_purpose_ok</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Worth pinning down whether you have a comparison group. It changes what is possible here.</t>
+          <t>Built for a different purpose</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>short_question_ok</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Answers a different question</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>short_maturity_min</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Program is too new</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>short_maturity_max</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Program is past this stage</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>short_data_level_min</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Needs data you do not have</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>short_comparison_required</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Needs a comparison group</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>short_fidelity_ok</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Wrong fit for how this program runs</t>
         </is>
       </c>
     </row>
